--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -23855,13 +23855,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="O142" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="R142" t="n">
-        <v>0.2810056389498466</v>
+        <v>0.2848815787974308</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="O165" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="R165" t="n">
-        <v>0.0891466164944341</v>
+        <v>0.1007744360371864</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -27607,12 +27607,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27646,81 +27646,100 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="O166" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="R166" t="n">
-        <v>0.0825130982237583</v>
+        <v>1.420421825099069</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27747,17 +27766,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27782,7 +27801,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M167" t="inlineStr">
@@ -27791,81 +27810,175 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O167" t="n">
-        <v>148</v>
-      </c>
-      <c r="R167" t="n">
-        <v>0.1208876443197334</v>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD167" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE167" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN167" t="b">
+        <v>1</v>
       </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT167" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -27927,7 +28040,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M168" t="inlineStr">
@@ -27936,13 +28049,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="O168" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="R168" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28072,7 +28185,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28081,13 +28194,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O169" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="R169" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -28217,7 +28330,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28226,13 +28339,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="O170" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="R170" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -28362,7 +28475,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28371,13 +28484,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="O171" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="R171" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.1168036022819046</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -28507,7 +28620,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -28516,13 +28629,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="O172" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="R172" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.07993456390426584</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -28652,7 +28765,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -28661,13 +28774,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="O173" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="R173" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.1453918965467064</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -28797,7 +28910,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -28806,13 +28919,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O174" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R174" t="n">
-        <v>0.07162595331923463</v>
+        <v>0.07133944950595769</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -28912,12 +29025,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -28942,22 +29055,22 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N175" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="O175" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="R175" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -28990,42 +29103,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29057,12 +29170,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29087,109 +29200,90 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N176" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="O176" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="R176" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.07162595331923463</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA176" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ176" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR176" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS176" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29216,17 +29310,17 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29265,170 +29359,76 @@
       <c r="O177" t="n">
         <v>1</v>
       </c>
-      <c r="U177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W177" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X177" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y177" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z177" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA177" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB177" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC177" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD177" t="inlineStr">
+      <c r="R177" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP177" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR177" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS177" t="inlineStr"/>
+      <c r="AT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV177" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE177" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF177" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG177" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH177" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI177" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ177" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK177" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM177" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN177" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP177" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ177" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS177" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT177" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV177" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29460,118 +29460,521 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N178" t="n">
+        <v>1</v>
+      </c>
+      <c r="O178" t="n">
+        <v>1</v>
+      </c>
+      <c r="R178" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO178" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP178" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ178" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR178" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT178" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU178" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV178" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW178" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX178" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY178" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA178" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB178" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC178" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N179" t="n">
+        <v>1</v>
+      </c>
+      <c r="O179" t="n">
+        <v>1</v>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD179" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE179" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN179" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR179" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT179" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU179" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV179" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW179" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX179" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY179" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA179" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB179" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC179" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G178" t="inlineStr">
+      <c r="G180" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>D115</t>
-        </is>
-      </c>
-      <c r="I178" t="inlineStr">
-        <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
-        </is>
-      </c>
-      <c r="J178" t="inlineStr">
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
         <is>
           <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr">
+      <c r="L180" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr">
+      <c r="M180" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N178" t="n">
+      <c r="N180" t="n">
         <v>0</v>
       </c>
-      <c r="O178" t="n">
+      <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="R178" t="n">
+      <c r="R180" t="n">
         <v>0</v>
       </c>
-      <c r="S178" t="inlineStr">
+      <c r="S180" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO178" t="inlineStr">
+      <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP178" t="inlineStr">
+      <c r="AP180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR178" t="inlineStr">
+      <c r="AR180" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS178" t="inlineStr"/>
-      <c r="AT178" t="n">
+      <c r="AS180" t="inlineStr"/>
+      <c r="AT180" t="n">
         <v>0</v>
       </c>
-      <c r="AU178" t="inlineStr">
+      <c r="AU180" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV178" t="inlineStr">
+      <c r="AV180" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW178" t="inlineStr">
+      <c r="AW180" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX178" t="inlineStr">
+      <c r="AX180" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY178" t="inlineStr">
+      <c r="AY180" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ178" t="inlineStr">
+      <c r="AZ180" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA178" t="inlineStr">
+      <c r="BA180" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB178" t="inlineStr">
+      <c r="BB180" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC178" t="inlineStr">
+      <c r="BC180" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -29693,7 +30096,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10">
@@ -29703,7 +30106,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11">
@@ -29723,7 +30126,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -29755,7 +30158,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11554</v>
+        <v>11714</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -26101,13 +26101,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="O156" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1138571664051135</v>
+        <v>0.1285484136831927</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="O165" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="R165" t="n">
-        <v>0.1007744360371864</v>
+        <v>0.1085263157323546</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -29315,12 +29315,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29345,22 +29345,22 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N177" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="O177" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="R177" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.1666289151434163</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29393,42 +29393,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29460,12 +29460,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29505,94 +29505,75 @@
         <v>1</v>
       </c>
       <c r="R178" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA178" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ178" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR178" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS178" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -29619,7 +29600,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -29663,103 +29644,28 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O179" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R179" t="n">
+        <v>0.03557618341728275</v>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U179" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
-      <c r="V179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W179" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X179" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y179" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z179" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB179" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC179" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD179" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE179" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF179" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG179" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH179" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI179" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ179" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK179" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM179" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN179" t="b">
-        <v>1</v>
       </c>
       <c r="AO179" t="inlineStr">
         <is>
@@ -29858,123 +29764,362 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N180" t="n">
+        <v>2</v>
+      </c>
+      <c r="O180" t="n">
+        <v>2</v>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD180" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE180" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF180" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG180" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH180" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI180" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM180" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN180" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO180" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP180" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ180" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR180" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT180" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU180" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV180" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW180" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX180" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY180" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA180" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB180" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC180" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
           <t>public_projection</t>
         </is>
       </c>
-      <c r="F180" t="inlineStr">
+      <c r="F181" t="inlineStr">
         <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>D115</t>
-        </is>
-      </c>
-      <c r="I180" t="inlineStr">
-        <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
-        </is>
-      </c>
-      <c r="J180" t="inlineStr">
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
         <is>
           <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
+      <c r="K181" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr">
+      <c r="L181" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr">
+      <c r="M181" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N180" t="n">
+      <c r="N181" t="n">
         <v>0</v>
       </c>
-      <c r="O180" t="n">
+      <c r="O181" t="n">
         <v>0</v>
       </c>
-      <c r="R180" t="n">
+      <c r="R181" t="n">
         <v>0</v>
       </c>
-      <c r="S180" t="inlineStr">
+      <c r="S181" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO180" t="inlineStr">
+      <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP180" t="inlineStr">
+      <c r="AP181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR180" t="inlineStr">
+      <c r="AR181" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS180" t="inlineStr"/>
-      <c r="AT180" t="n">
+      <c r="AS181" t="inlineStr"/>
+      <c r="AT181" t="n">
         <v>0</v>
       </c>
-      <c r="AU180" t="inlineStr">
+      <c r="AU181" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV180" t="inlineStr">
+      <c r="AV181" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW180" t="inlineStr">
+      <c r="AW181" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX180" t="inlineStr">
+      <c r="AX181" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY180" t="inlineStr">
+      <c r="AY181" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ180" t="inlineStr">
+      <c r="AZ181" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA180" t="inlineStr">
+      <c r="BA181" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB180" t="inlineStr">
+      <c r="BB181" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC180" t="inlineStr">
+      <c r="BC181" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -30096,7 +30241,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
@@ -30106,7 +30251,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -30158,7 +30303,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11714</v>
+        <v>11927</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -26101,13 +26101,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O156" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1285484136831927</v>
+        <v>0.1322212255027125</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27501,13 +27501,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="O165" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="R165" t="n">
-        <v>0.1085263157323546</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -29644,13 +29644,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O179" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="R179" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O180" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
@@ -30303,7 +30303,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11927</v>
+        <v>11935</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -29644,13 +29644,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O179" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="R179" t="n">
-        <v>0.1067285502518482</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -29808,10 +29808,10 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O180" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
@@ -30122,6 +30122,151 @@
       <c r="BC181" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>241</v>
+      </c>
+      <c r="O182" t="n">
+        <v>241</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.06904741899974219</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30158,7 +30303,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -30241,7 +30386,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10">
@@ -30251,7 +30396,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="11">
@@ -30303,7 +30448,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>11935</v>
+        <v>12178</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="N66" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O66" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R66" t="n">
-        <v>1.232265643612346</v>
+        <v>1.243367135897142</v>
       </c>
       <c r="S66" t="inlineStr">
         <is>
@@ -14873,13 +14873,13 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="O86" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="R86" t="n">
-        <v>1.476498473877856</v>
+        <v>1.532005935301835</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -18981,10 +18981,10 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O112" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="S112" t="inlineStr">
         <is>
@@ -19137,10 +19137,10 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="O113" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="U113" t="inlineStr">
         <is>
@@ -19371,13 +19371,13 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O114" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R114" t="n">
-        <v>1.820644734706529</v>
+        <v>1.831746226991325</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
@@ -23123,12 +23123,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -23162,81 +23162,92 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>243</v>
+        <v>36</v>
       </c>
       <c r="O138" t="n">
-        <v>243</v>
-      </c>
-      <c r="R138" t="n">
-        <v>2.697662625205405</v>
+        <v>36</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS138" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23263,17 +23274,17 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -23307,22 +23318,39 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O139" t="n">
-        <v>34</v>
-      </c>
-      <c r="R139" t="n">
-        <v>0.6047951180938068</v>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>36</v>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Verotoxin Producing E. Coli Including HUS</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -23330,6 +23358,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary culture-confirmed verotoxin-producing Escherichia coli infection notifications. Although the source title mentions HUS, probable HUS-only, toxin-only and NAAT-only cases are excluded from July 2026 IDTO totals.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>1</v>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -23337,70 +23423,65 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
         </is>
       </c>
       <c r="AT139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -23427,17 +23508,17 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -23471,175 +23552,81 @@
         </is>
       </c>
       <c r="N140" t="n">
-        <v>34</v>
+        <v>267</v>
       </c>
       <c r="O140" t="n">
-        <v>34</v>
-      </c>
-      <c r="U140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W140" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X140" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y140" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z140" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA140" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB140" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD140" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE140" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF140" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG140" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH140" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI140" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN140" t="b">
-        <v>1</v>
+        <v>267</v>
+      </c>
+      <c r="R140" t="n">
+        <v>2.964098440040507</v>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ140" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR140" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS140" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -23671,12 +23658,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -23710,81 +23697,100 @@
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O141" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="R141" t="n">
-        <v>0</v>
+        <v>0.6047951180938068</v>
       </c>
       <c r="S141" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS141" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT141" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23811,17 +23817,17 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -23855,81 +23861,175 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="O142" t="n">
-        <v>147</v>
-      </c>
-      <c r="R142" t="n">
-        <v>0.2848815787974308</v>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>34</v>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD142" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE142" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF142" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG142" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH142" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI142" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN142" t="b">
+        <v>1</v>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS142" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT142" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -23961,12 +24061,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -24000,95 +24100,81 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="O143" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="R143" t="n">
-        <v>1.210406698541971</v>
+        <v>0</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -24115,17 +24201,17 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -24159,170 +24245,81 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>64</v>
+        <v>147</v>
       </c>
       <c r="O144" t="n">
-        <v>64</v>
-      </c>
-      <c r="U144" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA144" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="R144" t="n">
+        <v>0.2848815787974308</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ144" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS144" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -24354,12 +24351,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -24393,13 +24390,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="O145" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="R145" t="n">
-        <v>1.168110053535418</v>
+        <v>1.210406698541971</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24408,7 +24405,7 @@
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -24423,7 +24420,7 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
@@ -24431,62 +24428,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24518,12 +24510,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -24557,29 +24549,29 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="O146" t="n">
-        <v>125</v>
+        <v>64</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="V146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="W146" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>VTEC/STEC infection</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -24589,7 +24581,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -24604,7 +24596,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr">
@@ -24639,17 +24631,17 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN146" t="b">
@@ -24662,7 +24654,7 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
@@ -24670,62 +24662,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -24757,12 +24744,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -24787,7 +24774,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -24796,81 +24783,100 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O147" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R147" t="n">
-        <v>0.1004674341305892</v>
+        <v>1.168110053535418</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT147" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -24897,17 +24903,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -24932,7 +24938,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -24941,81 +24947,175 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>168</v>
+        <v>125</v>
       </c>
       <c r="O148" t="n">
-        <v>168</v>
-      </c>
-      <c r="R148" t="n">
-        <v>0.04813264063052567</v>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD148" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE148" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF148" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG148" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH148" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM148" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN148" t="b">
+        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS148" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -25077,7 +25177,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -25086,13 +25186,13 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="O149" t="n">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="R149" t="n">
-        <v>0.08086403234901086</v>
+        <v>0.1004674341305892</v>
       </c>
       <c r="S149" t="inlineStr">
         <is>
@@ -25222,7 +25322,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -25231,13 +25331,13 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="O150" t="n">
-        <v>215</v>
+        <v>168</v>
       </c>
       <c r="R150" t="n">
-        <v>0.06159831985454178</v>
+        <v>0.04813264063052567</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -25367,7 +25467,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -25376,13 +25476,13 @@
         </is>
       </c>
       <c r="N151" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="O151" t="n">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="R151" t="n">
-        <v>0.0677950978279586</v>
+        <v>0.08086403234901086</v>
       </c>
       <c r="S151" t="inlineStr">
         <is>
@@ -25512,7 +25612,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -25521,13 +25621,13 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="O152" t="n">
-        <v>287</v>
+        <v>215</v>
       </c>
       <c r="R152" t="n">
-        <v>0.08222659441048136</v>
+        <v>0.06159831985454178</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -25657,7 +25757,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -25666,13 +25766,13 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="O153" t="n">
-        <v>126</v>
+        <v>83</v>
       </c>
       <c r="R153" t="n">
-        <v>0.1029178593532865</v>
+        <v>0.0677950978279586</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
@@ -25802,7 +25902,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -25811,13 +25911,13 @@
         </is>
       </c>
       <c r="N154" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="O154" t="n">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="R154" t="n">
-        <v>0.08509163254325074</v>
+        <v>0.08222659441048136</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -25947,7 +26047,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -25956,13 +26056,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="O155" t="n">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="R155" t="n">
-        <v>0.08821530801710276</v>
+        <v>0.1029178593532865</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -26062,12 +26162,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -26092,22 +26192,22 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N156" t="n">
-        <v>36</v>
+        <v>297</v>
       </c>
       <c r="O156" t="n">
-        <v>36</v>
+        <v>297</v>
       </c>
       <c r="R156" t="n">
-        <v>0.1322212255027125</v>
+        <v>0.08509163254325074</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -26140,42 +26240,42 @@
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -26207,12 +26307,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -26237,23 +26337,26 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>108</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>108</v>
+      </c>
+      <c r="R157" t="n">
+        <v>0.08821530801710276</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -26282,42 +26385,42 @@
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26349,12 +26452,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -26388,14 +26491,17 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="O158" t="n">
-        <v>6</v>
+        <v>36</v>
+      </c>
+      <c r="R158" t="n">
+        <v>0.1322212255027125</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO158" t="inlineStr">
@@ -26429,12 +26535,12 @@
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
@@ -26449,12 +26555,12 @@
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
@@ -26491,12 +26597,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -26571,7 +26677,7 @@
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
@@ -26591,7 +26697,7 @@
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
@@ -26633,12 +26739,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -26672,10 +26778,10 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="O160" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -26713,7 +26819,7 @@
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
@@ -26733,7 +26839,7 @@
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
@@ -26775,12 +26881,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -26855,7 +26961,7 @@
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
@@ -26875,7 +26981,7 @@
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
@@ -26917,12 +27023,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -26997,7 +27103,7 @@
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
@@ -27017,7 +27123,7 @@
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
@@ -27059,12 +27165,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -27098,100 +27204,78 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="O163" t="n">
-        <v>57</v>
-      </c>
-      <c r="R163" t="n">
-        <v>1.013921227392558</v>
+        <v>0</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA163" t="inlineStr">
-        <is>
-          <t>monthly</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ163" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS163" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27218,17 +27302,17 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -27262,175 +27346,78 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="O164" t="n">
-        <v>57</v>
-      </c>
-      <c r="U164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W164" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X164" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y164" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD164" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV164" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE164" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF164" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG164" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH164" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI164" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM164" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN164" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT164" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV164" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27462,12 +27449,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -27501,13 +27488,13 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>59</v>
+        <v>261</v>
       </c>
       <c r="O165" t="n">
-        <v>59</v>
+        <v>261</v>
       </c>
       <c r="R165" t="n">
-        <v>0.1143402255037307</v>
+        <v>2.897489486331732</v>
       </c>
       <c r="S165" t="inlineStr">
         <is>
@@ -27540,42 +27527,42 @@
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -27607,12 +27594,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -27646,13 +27633,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="O166" t="n">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="R166" t="n">
-        <v>1.420421825099069</v>
+        <v>1.013921227392558</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -27661,7 +27648,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -27681,7 +27668,7 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR166" t="inlineStr">
@@ -27691,7 +27678,7 @@
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT166" t="n">
@@ -27699,47 +27686,47 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27771,12 +27758,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -27810,29 +27797,29 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="O167" t="n">
-        <v>152</v>
+        <v>57</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>EHEC</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -27857,7 +27844,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -27892,17 +27879,17 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -27920,7 +27907,7 @@
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR167" t="inlineStr">
@@ -27930,7 +27917,7 @@
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
       <c r="AT167" t="n">
@@ -27938,47 +27925,47 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28010,12 +27997,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28049,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>288</v>
+        <v>59</v>
       </c>
       <c r="O168" t="n">
-        <v>288</v>
+        <v>59</v>
       </c>
       <c r="R168" t="n">
-        <v>0.0825130982237583</v>
+        <v>0.1143402255037307</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28088,42 +28075,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28155,12 +28142,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28185,7 +28172,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -28194,81 +28181,100 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O169" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="R169" t="n">
-        <v>0.1208876443197334</v>
+        <v>1.420421825099069</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR169" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28295,17 +28301,17 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28330,7 +28336,7 @@
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M170" t="inlineStr">
@@ -28339,81 +28345,175 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>310</v>
+        <v>152</v>
       </c>
       <c r="O170" t="n">
-        <v>310</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0.08881618211585095</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD170" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE170" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF170" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG170" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH170" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI170" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM170" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN170" t="b">
+        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ170" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR170" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT170" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28445,12 +28545,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28475,7 +28575,7 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
@@ -28484,13 +28584,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>143</v>
+        <v>288</v>
       </c>
       <c r="O171" t="n">
-        <v>143</v>
+        <v>288</v>
       </c>
       <c r="R171" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -28523,42 +28623,42 @@
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28590,12 +28690,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -28620,7 +28720,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -28629,13 +28729,13 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>279</v>
+        <v>148</v>
       </c>
       <c r="O172" t="n">
-        <v>279</v>
+        <v>148</v>
       </c>
       <c r="R172" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -28668,42 +28768,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28735,12 +28835,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -28765,7 +28865,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -28774,13 +28874,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>178</v>
+        <v>310</v>
       </c>
       <c r="O173" t="n">
-        <v>178</v>
+        <v>310</v>
       </c>
       <c r="R173" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -28813,42 +28913,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28880,12 +28980,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -28910,7 +29010,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -28919,13 +29019,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="O174" t="n">
-        <v>249</v>
+        <v>143</v>
       </c>
       <c r="R174" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.1168036022819046</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -28958,42 +29058,42 @@
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29025,12 +29125,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29055,7 +29155,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29064,13 +29164,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="O175" t="n">
-        <v>213</v>
+        <v>279</v>
       </c>
       <c r="R175" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.07993456390426584</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29103,42 +29203,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29170,12 +29270,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29200,7 +29300,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29209,13 +29309,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="O176" t="n">
-        <v>250</v>
+        <v>178</v>
       </c>
       <c r="R176" t="n">
-        <v>0.07162595331923463</v>
+        <v>0.1453918965467064</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29248,42 +29348,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29315,12 +29415,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29345,7 +29445,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29354,13 +29454,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="O177" t="n">
-        <v>204</v>
+        <v>249</v>
       </c>
       <c r="R177" t="n">
-        <v>0.1666289151434163</v>
+        <v>0.07133944950595769</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29393,42 +29493,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29460,12 +29560,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29490,22 +29590,22 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N178" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="O178" t="n">
-        <v>1</v>
+        <v>213</v>
       </c>
       <c r="R178" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -29538,42 +29638,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29605,12 +29705,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29635,109 +29735,90 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N179" t="n">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="O179" t="n">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="R179" t="n">
-        <v>0.142304733669131</v>
+        <v>0.07162595331923463</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA179" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ179" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR179" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS179" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29764,17 +29845,17 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29799,184 +29880,90 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N180" t="n">
-        <v>8</v>
+        <v>204</v>
       </c>
       <c r="O180" t="n">
-        <v>8</v>
-      </c>
-      <c r="U180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X180" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y180" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z180" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA180" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB180" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD180" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE180" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF180" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG180" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH180" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI180" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ180" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK180" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM180" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN180" t="b">
-        <v>1</v>
+        <v>204</v>
+      </c>
+      <c r="R180" t="n">
+        <v>0.1666289151434163</v>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ180" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS180" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30008,12 +29995,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30047,13 +30034,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R181" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -30086,42 +30073,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30153,118 +30140,666 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>8</v>
+      </c>
+      <c r="O182" t="n">
+        <v>8</v>
+      </c>
+      <c r="R182" t="n">
+        <v>0.142304733669131</v>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO182" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP182" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ182" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR182" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT182" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU182" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV182" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW182" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX182" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY182" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA182" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB182" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC182" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>8</v>
+      </c>
+      <c r="O183" t="n">
+        <v>8</v>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD183" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE183" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF183" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG183" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH183" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI183" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM183" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN183" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ183" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT183" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA183" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB183" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC183" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="O184" t="n">
+        <v>0</v>
+      </c>
+      <c r="R184" t="n">
+        <v>0</v>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO184" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP184" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR184" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
+      <c r="AT184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV184" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB184" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC184" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G182" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>D115</t>
-        </is>
-      </c>
-      <c r="I182" t="inlineStr">
-        <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
-        </is>
-      </c>
-      <c r="J182" t="inlineStr">
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
         <is>
           <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
+      <c r="L185" t="inlineStr">
         <is>
           <t>2026-09-05</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr">
+      <c r="M185" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N182" t="n">
+      <c r="N185" t="n">
         <v>241</v>
       </c>
-      <c r="O182" t="n">
+      <c r="O185" t="n">
         <v>241</v>
       </c>
-      <c r="R182" t="n">
+      <c r="R185" t="n">
         <v>0.06904741899974219</v>
       </c>
-      <c r="S182" t="inlineStr">
+      <c r="S185" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO182" t="inlineStr">
+      <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP182" t="inlineStr">
+      <c r="AP185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR182" t="inlineStr">
+      <c r="AR185" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS182" t="inlineStr"/>
-      <c r="AT182" t="n">
+      <c r="AS185" t="inlineStr"/>
+      <c r="AT185" t="n">
         <v>0</v>
       </c>
-      <c r="AU182" t="inlineStr">
+      <c r="AU185" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV182" t="inlineStr">
+      <c r="AV185" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW182" t="inlineStr">
+      <c r="AW185" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX182" t="inlineStr">
+      <c r="AX185" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY182" t="inlineStr">
+      <c r="AY185" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ182" t="inlineStr">
+      <c r="AZ185" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA182" t="inlineStr">
+      <c r="BA185" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB182" t="inlineStr">
+      <c r="BB185" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC182" t="inlineStr">
+      <c r="BC185" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -30386,7 +30921,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -30396,7 +30931,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -30416,7 +30951,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13">
@@ -30448,7 +30983,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12178</v>
+        <v>12507</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -26491,13 +26491,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O158" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="R158" t="n">
-        <v>0.1322212255027125</v>
+        <v>0.139566849141752</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="O168" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1143402255037307</v>
+        <v>0.1240300751226909</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12507</v>
+        <v>12514</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -26491,13 +26491,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="O158" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R158" t="n">
-        <v>0.139566849141752</v>
+        <v>0.1469124727807916</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -30983,7 +30983,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12514</v>
+        <v>12516</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="O168" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1240300751226909</v>
+        <v>0.1395338345130273</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -30179,13 +30179,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O182" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R182" t="n">
-        <v>0.142304733669131</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -30343,10 +30343,10 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O183" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -30582,13 +30582,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R184" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -30802,6 +30802,151 @@
       <c r="BC185" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>137</v>
+      </c>
+      <c r="O186" t="n">
+        <v>137</v>
+      </c>
+      <c r="R186" t="n">
+        <v>0.11190275183651</v>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO186" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP186" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR186" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr"/>
+      <c r="AT186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU186" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV186" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30838,7 +30983,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -30921,7 +31066,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10">
@@ -30931,7 +31076,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -30983,7 +31128,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12516</v>
+        <v>12665</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -24390,13 +24390,13 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O145" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="R145" t="n">
-        <v>1.210406698541971</v>
+        <v>1.191494093877252</v>
       </c>
       <c r="S145" t="inlineStr">
         <is>
@@ -24549,10 +24549,10 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="O146" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="O168" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1395338345130273</v>
+        <v>0.1511616540557796</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28142,12 +28142,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28181,13 +28181,13 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="O169" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="R169" t="n">
-        <v>1.420421825099069</v>
+        <v>1.683221815159928</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -28211,7 +28211,7 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ169" t="inlineStr">
@@ -28219,62 +28219,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT169" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28306,12 +28301,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -28345,29 +28340,29 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="O170" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="V170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="W170" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X170" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>VTEC/STEC infection</t>
         </is>
       </c>
       <c r="Y170" t="inlineStr">
@@ -28377,7 +28372,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -28392,7 +28387,7 @@
       </c>
       <c r="AC170" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD170" t="inlineStr">
@@ -28427,17 +28422,17 @@
       </c>
       <c r="AJ170" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK170" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
         </is>
       </c>
       <c r="AM170" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN170" t="b">
@@ -28450,7 +28445,7 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ170" t="inlineStr">
@@ -28458,62 +28453,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28545,12 +28535,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28584,81 +28574,100 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="O171" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="R171" t="n">
-        <v>0.0825130982237583</v>
+        <v>1.420421825099069</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ171" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR171" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS171" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS171" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT171" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28685,17 +28694,17 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -28720,7 +28729,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -28729,81 +28738,175 @@
         </is>
       </c>
       <c r="N172" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O172" t="n">
-        <v>148</v>
-      </c>
-      <c r="R172" t="n">
-        <v>0.1208876443197334</v>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR172" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS172" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT172" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -28865,7 +28968,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -28874,13 +28977,13 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="O173" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="R173" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S173" t="inlineStr">
         <is>
@@ -29010,7 +29113,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29019,13 +29122,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O174" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="R174" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29155,7 +29258,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29164,13 +29267,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="O175" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="R175" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29300,7 +29403,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29309,13 +29412,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="O176" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="R176" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.1168036022819046</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29445,7 +29548,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29454,13 +29557,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="O177" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="R177" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.07993456390426584</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29590,7 +29693,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -29599,13 +29702,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="O178" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="R178" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.1453918965467064</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -29735,7 +29838,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -29744,13 +29847,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O179" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R179" t="n">
-        <v>0.07162595331923463</v>
+        <v>0.07133944950595769</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -29880,7 +29983,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -29889,13 +29992,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="O180" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R180" t="n">
-        <v>0.1666289151434163</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -29995,12 +30098,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30025,22 +30128,22 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N181" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="O181" t="n">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="R181" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.07162595331923463</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -30073,42 +30176,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30140,12 +30243,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30170,109 +30273,90 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N182" t="n">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="O182" t="n">
-        <v>11</v>
+        <v>204</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.1666289151434163</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA182" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ182" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS182" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30299,17 +30383,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30343,175 +30427,81 @@
         </is>
       </c>
       <c r="N183" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O183" t="n">
-        <v>11</v>
-      </c>
-      <c r="U183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X183" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y183" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z183" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA183" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB183" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD183" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="R183" t="n">
+        <v>0.00367281181951979</v>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP183" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR183" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS183" t="inlineStr"/>
+      <c r="AT183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU183" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV183" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE183" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF183" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG183" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH183" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI183" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ183" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK183" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM183" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN183" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP183" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ183" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS183" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT183" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV183" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30543,12 +30533,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -30582,81 +30572,100 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="O184" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="R184" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.1956690087950551</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ184" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT184" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30683,17 +30692,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -30718,7 +30727,7 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
@@ -30727,81 +30736,175 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>241</v>
+        <v>11</v>
       </c>
       <c r="O185" t="n">
-        <v>241</v>
-      </c>
-      <c r="R185" t="n">
-        <v>0.06904741899974219</v>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>11</v>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD185" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE185" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF185" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG185" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH185" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI185" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM185" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN185" t="b">
+        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ185" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS185" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS185" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT185" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -30833,12 +30936,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -30863,7 +30966,7 @@
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M186" t="inlineStr">
@@ -30872,13 +30975,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="O186" t="n">
-        <v>137</v>
+        <v>5</v>
       </c>
       <c r="R186" t="n">
-        <v>0.11190275183651</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -30911,40 +31014,330 @@
       </c>
       <c r="AV186" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA186" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB186" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC186" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N187" t="n">
+        <v>241</v>
+      </c>
+      <c r="O187" t="n">
+        <v>241</v>
+      </c>
+      <c r="R187" t="n">
+        <v>0.06904741899974219</v>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP187" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR187" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS187" t="inlineStr"/>
+      <c r="AT187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU187" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV187" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA187" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB187" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC187" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N188" t="n">
+        <v>137</v>
+      </c>
+      <c r="O188" t="n">
+        <v>137</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0.11190275183651</v>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP188" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR188" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS188" t="inlineStr"/>
+      <c r="AT188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU188" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV188" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW186" t="inlineStr">
+      <c r="AW188" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX186" t="inlineStr">
+      <c r="AX188" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY186" t="inlineStr">
+      <c r="AY188" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ186" t="inlineStr">
+      <c r="AZ188" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA186" t="inlineStr">
+      <c r="BA188" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB186" t="inlineStr">
+      <c r="BB188" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC186" t="inlineStr">
+      <c r="BC188" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -31066,7 +31459,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10">
@@ -31076,7 +31469,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11">
@@ -31096,7 +31489,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -31128,7 +31521,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12665</v>
+        <v>12763</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -30572,13 +30572,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O184" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="R184" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -30736,10 +30736,10 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="O185" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12763</v>
+        <v>12768</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="O168" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1511616540557796</v>
+        <v>0.1530996239795716</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -30975,13 +30975,13 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O186" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R186" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
@@ -31340,6 +31340,151 @@
       <c r="BC188" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N189" t="n">
+        <v>199</v>
+      </c>
+      <c r="O189" t="n">
+        <v>199</v>
+      </c>
+      <c r="R189" t="n">
+        <v>0.05701425884211077</v>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP189" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR189" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS189" t="inlineStr"/>
+      <c r="AT189" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU189" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV189" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31376,7 +31521,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -31459,7 +31604,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="10">
@@ -31469,7 +31614,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -31521,7 +31666,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12768</v>
+        <v>12979</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O168" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1530996239795716</v>
+        <v>0.1550375939033637</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12979</v>
+        <v>12980</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -26491,13 +26491,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="O158" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R158" t="n">
-        <v>0.1469124727807916</v>
+        <v>0.1505852846003114</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -27997,12 +27997,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -28036,13 +28036,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="O168" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0.1550375939033637</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -28075,42 +28075,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28142,12 +28142,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -28181,95 +28181,81 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="O169" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="R169" t="n">
-        <v>1.683221815159928</v>
+        <v>0.1608515036747398</v>
       </c>
       <c r="S169" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA169" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ169" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR169" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28296,7 +28282,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -28345,98 +28331,23 @@
       <c r="O170" t="n">
         <v>89</v>
       </c>
+      <c r="R170" t="n">
+        <v>1.683221815159928</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U170" t="inlineStr">
         <is>
           <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
-      <c r="V170" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X170" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y170" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z170" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB170" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC170" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD170" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE170" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF170" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG170" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH170" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI170" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM170" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN170" t="b">
-        <v>1</v>
       </c>
       <c r="AO170" t="inlineStr">
         <is>
@@ -28530,17 +28441,17 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -28574,22 +28485,39 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="O171" t="n">
-        <v>152</v>
-      </c>
-      <c r="R171" t="n">
-        <v>1.420421825099069</v>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>89</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC_NZ_PHS</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>VTEC/STEC infection</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -28597,6 +28525,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr">
+        <is>
+          <t>country:NZ:national</t>
+        </is>
+      </c>
+      <c r="AD171" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE171" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF171" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG171" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH171" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI171" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>NZ_PHS_current</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
+        </is>
+      </c>
+      <c r="AM171" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN171" t="b">
+        <v>1</v>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -28604,7 +28590,7 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ171" t="inlineStr">
@@ -28612,62 +28598,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU171" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28694,7 +28675,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -28743,98 +28724,23 @@
       <c r="O172" t="n">
         <v>152</v>
       </c>
+      <c r="R172" t="n">
+        <v>1.420421825099069</v>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U172" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_EHEC</t>
         </is>
       </c>
-      <c r="V172" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
-        </is>
-      </c>
-      <c r="W172" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X172" t="inlineStr">
-        <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
-        </is>
-      </c>
-      <c r="Y172" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z172" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB172" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD172" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE172" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF172" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG172" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH172" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI172" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ172" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK172" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN172" t="b">
-        <v>1</v>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
@@ -28933,17 +28839,17 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -28977,81 +28883,175 @@
         </is>
       </c>
       <c r="N173" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="O173" t="n">
-        <v>288</v>
-      </c>
-      <c r="R173" t="n">
-        <v>0.0825130982237583</v>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD173" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE173" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF173" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG173" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH173" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI173" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM173" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN173" t="b">
+        <v>1</v>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ173" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS173" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS173" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT173" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29083,12 +29083,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -29113,7 +29113,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -29122,13 +29122,13 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="O174" t="n">
-        <v>148</v>
+        <v>288</v>
       </c>
       <c r="R174" t="n">
-        <v>0.1208876443197334</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -29161,42 +29161,42 @@
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29228,12 +29228,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -29258,7 +29258,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -29267,13 +29267,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="O175" t="n">
-        <v>310</v>
+        <v>148</v>
       </c>
       <c r="R175" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29306,42 +29306,42 @@
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29373,12 +29373,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -29403,7 +29403,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -29412,13 +29412,13 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="O176" t="n">
-        <v>143</v>
+        <v>310</v>
       </c>
       <c r="R176" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -29451,42 +29451,42 @@
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29518,12 +29518,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -29548,7 +29548,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -29557,13 +29557,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="O177" t="n">
-        <v>279</v>
+        <v>143</v>
       </c>
       <c r="R177" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.1168036022819046</v>
       </c>
       <c r="S177" t="inlineStr">
         <is>
@@ -29596,42 +29596,42 @@
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29663,12 +29663,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -29693,7 +29693,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -29702,13 +29702,13 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="O178" t="n">
-        <v>178</v>
+        <v>279</v>
       </c>
       <c r="R178" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.07993456390426584</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -29741,42 +29741,42 @@
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -29808,12 +29808,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -29838,7 +29838,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -29847,13 +29847,13 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="O179" t="n">
-        <v>249</v>
+        <v>178</v>
       </c>
       <c r="R179" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.1453918965467064</v>
       </c>
       <c r="S179" t="inlineStr">
         <is>
@@ -29886,42 +29886,42 @@
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29953,12 +29953,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -29983,7 +29983,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -29992,13 +29992,13 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="O180" t="n">
-        <v>213</v>
+        <v>249</v>
       </c>
       <c r="R180" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.07133944950595769</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -30031,42 +30031,42 @@
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30098,12 +30098,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -30128,7 +30128,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -30137,13 +30137,13 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="O181" t="n">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="R181" t="n">
-        <v>0.07162595331923463</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S181" t="inlineStr">
         <is>
@@ -30176,42 +30176,42 @@
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30243,12 +30243,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -30273,7 +30273,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -30282,13 +30282,13 @@
         </is>
       </c>
       <c r="N182" t="n">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="O182" t="n">
-        <v>204</v>
+        <v>250</v>
       </c>
       <c r="R182" t="n">
-        <v>0.1666289151434163</v>
+        <v>0.07162595331923463</v>
       </c>
       <c r="S182" t="inlineStr">
         <is>
@@ -30321,42 +30321,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30388,12 +30388,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -30418,22 +30418,22 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N183" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="O183" t="n">
-        <v>1</v>
+        <v>204</v>
       </c>
       <c r="R183" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.1666289151434163</v>
       </c>
       <c r="S183" t="inlineStr">
         <is>
@@ -30466,42 +30466,42 @@
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30533,12 +30533,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -30572,100 +30572,81 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="O184" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="R184" t="n">
-        <v>0.284609467338262</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AA184" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ184" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS184" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -30692,7 +30673,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -30736,103 +30717,28 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O185" t="n">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="R185" t="n">
+        <v>0.3735499258814688</v>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U185" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_535</t>
         </is>
       </c>
-      <c r="V185" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X185" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y185" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z185" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB185" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD185" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE185" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF185" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG185" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH185" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI185" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ185" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK185" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM185" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN185" t="b">
-        <v>1</v>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
@@ -30931,17 +30837,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -30975,81 +30881,175 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O186" t="n">
-        <v>16</v>
-      </c>
-      <c r="R186" t="n">
-        <v>0.03100751878067274</v>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD186" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE186" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF186" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG186" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH186" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI186" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM186" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN186" t="b">
+        <v>1</v>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ186" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS186" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS186" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT186" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -31081,12 +31081,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -31111,7 +31111,7 @@
       </c>
       <c r="L187" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M187" t="inlineStr">
@@ -31120,13 +31120,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>241</v>
+        <v>24</v>
       </c>
       <c r="O187" t="n">
-        <v>241</v>
+        <v>24</v>
       </c>
       <c r="R187" t="n">
-        <v>0.06904741899974219</v>
+        <v>0.0465112781710091</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -31159,42 +31159,42 @@
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31226,12 +31226,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -31256,7 +31256,7 @@
       </c>
       <c r="L188" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M188" t="inlineStr">
@@ -31265,13 +31265,13 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="O188" t="n">
-        <v>137</v>
+        <v>241</v>
       </c>
       <c r="R188" t="n">
-        <v>0.11190275183651</v>
+        <v>0.06904741899974219</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
@@ -31304,42 +31304,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31371,12 +31371,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -31401,7 +31401,7 @@
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M189" t="inlineStr">
@@ -31410,13 +31410,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="O189" t="n">
-        <v>199</v>
+        <v>137</v>
       </c>
       <c r="R189" t="n">
-        <v>0.05701425884211077</v>
+        <v>0.11190275183651</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -31449,40 +31449,475 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB189" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC189" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N190" t="n">
+        <v>199</v>
+      </c>
+      <c r="O190" t="n">
+        <v>199</v>
+      </c>
+      <c r="R190" t="n">
+        <v>0.05701425884211077</v>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP190" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR190" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS190" t="inlineStr"/>
+      <c r="AT190" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU190" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV190" t="inlineStr">
+        <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW189" t="inlineStr">
+      <c r="AW190" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX189" t="inlineStr">
+      <c r="AX190" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY189" t="inlineStr">
+      <c r="AY190" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ189" t="inlineStr">
+      <c r="AZ190" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA189" t="inlineStr">
+      <c r="BA190" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB189" t="inlineStr">
+      <c r="BB190" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC189" t="inlineStr">
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N191" t="n">
+        <v>148</v>
+      </c>
+      <c r="O191" t="n">
+        <v>148</v>
+      </c>
+      <c r="R191" t="n">
+        <v>0.1208876443197334</v>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO191" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP191" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR191" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS191" t="inlineStr"/>
+      <c r="AT191" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU191" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV191" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA191" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB191" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC191" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>165</v>
+      </c>
+      <c r="O192" t="n">
+        <v>165</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0.04727312919069485</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR192" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr"/>
+      <c r="AT192" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -31521,7 +31956,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -31604,7 +32039,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
@@ -31614,7 +32049,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11">
@@ -31666,7 +32101,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12980</v>
+        <v>13311</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -30572,13 +30572,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="O184" t="n">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="R184" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.2387327682687863</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -30717,13 +30717,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O185" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="R185" t="n">
-        <v>0.3735499258814688</v>
+        <v>0.5158546595505998</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -30881,10 +30881,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="O186" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -31120,13 +31120,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="O187" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="R187" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.06589097740892956</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -31920,6 +31920,844 @@
       <c r="BC192" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>147</v>
+      </c>
+      <c r="O193" t="n">
+        <v>147</v>
+      </c>
+      <c r="R193" t="n">
+        <v>0.1200708359121676</v>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR193" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr"/>
+      <c r="AT193" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N194" t="n">
+        <v>185</v>
+      </c>
+      <c r="O194" t="n">
+        <v>185</v>
+      </c>
+      <c r="R194" t="n">
+        <v>0.05300320545623363</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR194" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr"/>
+      <c r="AT194" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="n">
+        <v>0</v>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO195" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP195" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ195" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR195" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS195" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT195" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU195" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV195" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA195" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB195" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC195" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X196" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB196" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD196" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE196" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF196" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG196" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH196" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI196" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ196" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK196" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM196" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN196" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR196" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="R197" t="n">
+        <v>0</v>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR197" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr"/>
+      <c r="AT197" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -31956,7 +32794,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -32039,7 +32877,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10">
@@ -32049,7 +32887,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -32069,7 +32907,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -32101,7 +32939,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13311</v>
+        <v>13725</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -26491,13 +26491,13 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O158" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R158" t="n">
-        <v>0.1505852846003114</v>
+        <v>0.1542580964198312</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -30572,13 +30572,13 @@
         </is>
       </c>
       <c r="N184" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="O184" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="R184" t="n">
-        <v>0.2387327682687863</v>
+        <v>0.2497512037273457</v>
       </c>
       <c r="S184" t="inlineStr">
         <is>
@@ -31120,13 +31120,13 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O187" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R187" t="n">
-        <v>0.06589097740892956</v>
+        <v>0.06782894733272161</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13725</v>
+        <v>13730</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -30717,13 +30717,13 @@
         </is>
       </c>
       <c r="N185" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O185" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R185" t="n">
-        <v>0.5158546595505998</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S185" t="inlineStr">
         <is>
@@ -30881,10 +30881,10 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O186" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -32280,13 +32280,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R195" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -32444,10 +32444,10 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U196" t="inlineStr">
         <is>
@@ -32939,7 +32939,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13730</v>
+        <v>13732</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -38860,13 +38860,13 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="O241" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R241" t="n">
-        <v>0.07751879695168185</v>
+        <v>0.09108458641822616</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -40824,7 +40824,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14316</v>
+        <v>14323</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -912,6 +917,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1347,6 +1367,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1492,6 +1517,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1637,6 +1667,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1782,6 +1817,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1927,6 +1967,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2462,6 +2507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3010,6 +3060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3155,6 +3210,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4102,6 +4162,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4398,6 +4463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4694,6 +4764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4990,6 +5065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5286,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5434,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5570,6 +5660,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5715,6 +5810,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5860,6 +5960,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5996,6 +6101,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6141,6 +6251,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6277,6 +6392,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6422,6 +6542,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6567,6 +6692,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7102,6 +7232,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7650,6 +7785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7795,6 +7935,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8890,6 +9035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9186,6 +9336,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9482,6 +9637,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9778,6 +9938,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9926,6 +10091,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10062,6 +10232,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10207,6 +10382,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10352,6 +10532,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10497,6 +10682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10642,6 +10832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10778,6 +10973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10923,6 +11123,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11068,6 +11273,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11603,6 +11813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12151,6 +12366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12296,6 +12516,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13391,6 +13616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13687,6 +13917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13983,6 +14218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14279,6 +14519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14424,6 +14669,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14569,6 +14819,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14714,6 +14969,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14859,6 +15119,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15004,6 +15269,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15149,6 +15419,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15285,6 +15560,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15430,6 +15710,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15575,6 +15860,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16110,6 +16400,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16658,6 +16953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16803,6 +17103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17895,6 +18200,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18191,6 +18501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18487,6 +18802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18783,6 +19103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18928,6 +19253,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19073,6 +19403,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19218,6 +19553,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19363,6 +19703,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19508,6 +19853,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19653,6 +20003,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19789,6 +20144,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19934,6 +20294,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20079,6 +20444,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20211,10 +20581,10 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O124" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -20367,10 +20737,10 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O125" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
@@ -20614,6 +20984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21162,6 +21537,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21307,6 +21687,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22399,6 +22784,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22695,6 +23085,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22991,6 +23386,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23287,6 +23687,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23580,6 +23985,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23725,6 +24135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23870,6 +24285,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24015,6 +24435,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24151,6 +24576,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24296,6 +24726,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24441,6 +24876,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24577,6 +25017,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24722,6 +25167,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24867,6 +25317,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25402,6 +25857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25950,6 +26410,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26095,6 +26560,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27181,6 +27651,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27471,6 +27946,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27761,6 +28241,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28051,6 +28536,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28196,6 +28686,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28341,6 +28836,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28486,6 +28986,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28622,6 +29127,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28767,6 +29277,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28912,6 +29427,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29048,6 +29568,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29193,6 +29718,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29338,6 +29868,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29873,6 +30408,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30421,6 +30961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30566,6 +31111,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31652,6 +32202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31942,6 +32497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32232,6 +32792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32522,6 +33087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32812,6 +33382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32957,6 +33532,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33102,6 +33682,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33247,6 +33832,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33383,6 +33973,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33528,6 +34123,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33673,6 +34273,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33818,6 +34423,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33954,6 +34564,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34047,12 +34662,12 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
@@ -34086,81 +34701,92 @@
         </is>
       </c>
       <c r="N211" t="n">
-        <v>261</v>
+        <v>35</v>
       </c>
       <c r="O211" t="n">
-        <v>261</v>
-      </c>
-      <c r="R211" t="n">
-        <v>2.897489486331732</v>
+        <v>35</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS211" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ211" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS211" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU211" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV211" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ211" t="inlineStr">
         <is>
-          <t>foph_idd</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA211" t="inlineStr">
         <is>
-          <t>Switzerland FOPH IDD</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB211" t="inlineStr">
         <is>
-          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC211" t="inlineStr">
         <is>
-          <t>rest_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34187,17 +34813,17 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
@@ -34231,22 +34857,39 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="O212" t="n">
-        <v>57</v>
-      </c>
-      <c r="R212" t="n">
-        <v>1.013921227392558</v>
-      </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>35</v>
       </c>
       <c r="U212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V212" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W212" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X212" t="inlineStr">
+        <is>
+          <t>Verotoxin Producing E. Coli Including HUS</t>
+        </is>
+      </c>
+      <c r="Y212" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -34254,6 +34897,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB212" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC212" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD212" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE212" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF212" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG212" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH212" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI212" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ212" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK212" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary culture-confirmed verotoxin-producing Escherichia coli infection notifications. Although the source title mentions HUS, probable HUS-only, toxin-only and NAAT-only cases are excluded from July 2026 IDTO totals.</t>
+        </is>
+      </c>
+      <c r="AM212" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN212" t="b">
+        <v>1</v>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -34261,70 +34962,65 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ212" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>SER_CA_ON_PHO_IDTO_VEROTOXIN_ECOLI_INCLUDING_HUS_MONTHLY</t>
         </is>
       </c>
       <c r="AT212" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU212" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV212" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW212" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX212" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY212" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ212" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA212" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB212" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC212" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -34351,17 +35047,17 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
@@ -34395,39 +35091,17 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>57</v>
+        <v>261</v>
       </c>
       <c r="O213" t="n">
-        <v>57</v>
-      </c>
-      <c r="U213" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V213" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W213" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X213" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y213" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z213" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>261</v>
+      </c>
+      <c r="R213" t="n">
+        <v>2.897489486331732</v>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -34435,135 +35109,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB213" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC213" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD213" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE213" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF213" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG213" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH213" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI213" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ213" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK213" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM213" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN213" t="b">
-        <v>1</v>
-      </c>
       <c r="AO213" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ213" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR213" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS213" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU213" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV213" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW213" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX213" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY213" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ213" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA213" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB213" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC213" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -34595,12 +35202,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -34634,81 +35241,100 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="O214" t="n">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="R214" t="n">
-        <v>0.01355270280196709</v>
+        <v>1.013921227392558</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ214" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR214" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS214" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS214" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT214" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU214" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV214" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ214" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA214" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB214" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC214" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34735,17 +35361,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -34779,81 +35405,175 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="O215" t="n">
-        <v>83</v>
-      </c>
-      <c r="R215" t="n">
-        <v>0.1608515036747398</v>
-      </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>57</v>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W215" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X215" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y215" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB215" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC215" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD215" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE215" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF215" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG215" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH215" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI215" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ215" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK215" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM215" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN215" t="b">
+        <v>1</v>
       </c>
       <c r="AO215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ215" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR215" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS215" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS215" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT215" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU215" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV215" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ215" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA215" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB215" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC215" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -34885,12 +35605,12 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -34924,24 +35644,19 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="O216" t="n">
-        <v>89</v>
+        <v>1</v>
       </c>
       <c r="R216" t="n">
-        <v>1.683221815159928</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34949,70 +35664,66 @@
       </c>
       <c r="AO216" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ216" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS216" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR216" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU216" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV216" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW216" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX216" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY216" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ216" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA216" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB216" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC216" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -35039,17 +35750,17 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -35083,39 +35794,17 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="O217" t="n">
-        <v>89</v>
-      </c>
-      <c r="U217" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V217" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC_NZ_PHS</t>
-        </is>
-      </c>
-      <c r="X217" t="inlineStr">
-        <is>
-          <t>VTEC/STEC infection</t>
-        </is>
-      </c>
-      <c r="Y217" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z217" t="inlineStr">
-        <is>
-          <t>notification</t>
+        <v>83</v>
+      </c>
+      <c r="R217" t="n">
+        <v>0.1608515036747398</v>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -35123,130 +35812,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB217" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>country:NZ:national</t>
-        </is>
-      </c>
-      <c r="AD217" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE217" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF217" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG217" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH217" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI217" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ217" t="inlineStr">
-        <is>
-          <t>NZ_PHS_current</t>
-        </is>
-      </c>
-      <c r="AK217" t="inlineStr">
-        <is>
-          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
-        </is>
-      </c>
-      <c r="AM217" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN217" t="b">
-        <v>1</v>
-      </c>
       <c r="AO217" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ217" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS217" t="inlineStr">
-        <is>
-          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR217" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU217" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV217" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW217" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX217" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ217" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA217" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB217" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC217" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -35278,12 +35905,12 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -35317,13 +35944,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="O218" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="R218" t="n">
-        <v>1.420421825099069</v>
+        <v>1.683221815159928</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -35332,7 +35959,7 @@
       </c>
       <c r="U218" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -35347,7 +35974,7 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ218" t="inlineStr">
@@ -35355,62 +35982,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS218" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT218" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU218" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV218" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW218" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX218" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY218" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ218" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA218" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB218" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC218" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35442,12 +36064,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -35481,29 +36103,29 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="O219" t="n">
-        <v>152</v>
+        <v>89</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="V219" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="W219" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X219" t="inlineStr">
         <is>
-          <t>Enterohemorragisk E. coli-infektion</t>
+          <t>VTEC/STEC infection</t>
         </is>
       </c>
       <c r="Y219" t="inlineStr">
@@ -35513,7 +36135,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -35528,7 +36150,7 @@
       </c>
       <c r="AC219" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD219" t="inlineStr">
@@ -35563,17 +36185,17 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+          <t>New Zealand PHF Science monthly VTEC/STEC infection notifications.</t>
         </is>
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -35586,7 +36208,7 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ219" t="inlineStr">
@@ -35594,62 +36216,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS219" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_EHEC</t>
+          <t>SER_NZ_VTEC_STEC_MONTHLY</t>
         </is>
       </c>
       <c r="AT219" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU219" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV219" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW219" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX219" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY219" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ219" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA219" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB219" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC219" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35681,12 +36298,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -35720,81 +36337,100 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="O220" t="n">
-        <v>288</v>
+        <v>152</v>
       </c>
       <c r="R220" t="n">
-        <v>0.0825130982237583</v>
+        <v>1.420421825099069</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ220" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR220" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS220" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS220" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -35821,17 +36457,17 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -35856,7 +36492,7 @@
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M221" t="inlineStr">
@@ -35865,81 +36501,175 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="O221" t="n">
-        <v>148</v>
-      </c>
-      <c r="R221" t="n">
-        <v>0.1208876443197334</v>
-      </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X221" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y221" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB221" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD221" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE221" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF221" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG221" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH221" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI221" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ221" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK221" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM221" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN221" t="b">
+        <v>1</v>
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ221" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR221" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS221" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS221" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT221" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -36001,7 +36731,7 @@
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
@@ -36010,17 +36740,22 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="O222" t="n">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="R222" t="n">
-        <v>0.08881618211585095</v>
+        <v>0.0825130982237583</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO222" t="inlineStr">
@@ -36146,7 +36881,7 @@
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
@@ -36155,13 +36890,13 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="O223" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="R223" t="n">
-        <v>0.1168036022819046</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
@@ -36291,7 +37026,7 @@
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
@@ -36300,17 +37035,22 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="O224" t="n">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="R224" t="n">
-        <v>0.07993456390426584</v>
+        <v>0.08881618211585095</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO224" t="inlineStr">
@@ -36436,7 +37176,7 @@
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
@@ -36445,13 +37185,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="O225" t="n">
-        <v>178</v>
+        <v>143</v>
       </c>
       <c r="R225" t="n">
-        <v>0.1453918965467064</v>
+        <v>0.1168036022819046</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -36581,7 +37321,7 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
@@ -36590,17 +37330,22 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="O226" t="n">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="R226" t="n">
-        <v>0.07133944950595769</v>
+        <v>0.07993456390426584</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO226" t="inlineStr">
@@ -36726,7 +37471,7 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
@@ -36735,13 +37480,13 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="O227" t="n">
-        <v>213</v>
+        <v>178</v>
       </c>
       <c r="R227" t="n">
-        <v>0.1739801908115082</v>
+        <v>0.1453918965467064</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
@@ -36871,7 +37616,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -36880,17 +37625,22 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="O228" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="R228" t="n">
-        <v>0.07162595331923463</v>
+        <v>0.07133944950595769</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
@@ -37016,7 +37766,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -37025,13 +37775,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="O229" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="R229" t="n">
-        <v>0.1666289151434163</v>
+        <v>0.1739801908115082</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -37131,12 +37881,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -37161,26 +37911,31 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N230" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="O230" t="n">
-        <v>71</v>
+        <v>250</v>
       </c>
       <c r="R230" t="n">
-        <v>0.2607696391859051</v>
+        <v>0.07162595331923463</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -37209,42 +37964,42 @@
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -37276,12 +38031,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -37306,17 +38061,26 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>204</v>
+      </c>
+      <c r="O231" t="n">
+        <v>204</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.1666289151434163</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -37345,42 +38109,42 @@
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -37412,12 +38176,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -37451,17 +38215,22 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="O232" t="n">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="R232" t="n">
-        <v>0.138406628293429</v>
+        <v>0.2717880746444645</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -37495,12 +38264,12 @@
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
@@ -37515,12 +38284,12 @@
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
@@ -37557,12 +38326,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -37595,18 +38364,14 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N233" t="n">
-        <v>0</v>
-      </c>
-      <c r="O233" t="n">
-        <v>0</v>
-      </c>
-      <c r="R233" t="n">
-        <v>0</v>
-      </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO233" t="inlineStr">
@@ -37640,7 +38405,7 @@
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
@@ -37660,7 +38425,7 @@
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
@@ -37702,12 +38467,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -37741,17 +38506,22 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O234" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R234" t="n">
-        <v>0.1393859109766579</v>
+        <v>0.138406628293429</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO234" t="inlineStr">
@@ -37785,7 +38555,7 @@
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
@@ -37805,7 +38575,7 @@
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
@@ -37847,12 +38617,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -37886,17 +38656,22 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="R235" t="n">
-        <v>1.095555383976511</v>
+        <v>0</v>
       </c>
       <c r="S235" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO235" t="inlineStr">
@@ -37930,7 +38705,7 @@
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
@@ -37950,7 +38725,7 @@
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
@@ -37992,12 +38767,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -38030,9 +38805,23 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N236" t="n">
+        <v>8</v>
+      </c>
+      <c r="O236" t="n">
+        <v>8</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.1393859109766579</v>
+      </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO236" t="inlineStr">
@@ -38066,7 +38855,7 @@
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
@@ -38086,7 +38875,7 @@
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
@@ -38128,12 +38917,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -38167,17 +38956,22 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O237" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2236441955036055</v>
+        <v>1.095555383976511</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO237" t="inlineStr">
@@ -38211,7 +39005,7 @@
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
@@ -38231,7 +39025,7 @@
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
@@ -38273,12 +39067,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -38311,18 +39105,14 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N238" t="n">
-        <v>8</v>
-      </c>
-      <c r="O238" t="n">
-        <v>8</v>
-      </c>
-      <c r="R238" t="n">
-        <v>0.2583794056110963</v>
-      </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO238" t="inlineStr">
@@ -38356,7 +39146,7 @@
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
@@ -38376,7 +39166,7 @@
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
@@ -38418,12 +39208,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -38457,22 +39247,17 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="O239" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="R239" t="n">
-        <v>0.5336427512592412</v>
+        <v>0.2236441955036055</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U239" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -38482,75 +39267,66 @@
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ239" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR239" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS239" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38577,17 +39353,17 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -38621,39 +39397,17 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="O240" t="n">
-        <v>30</v>
-      </c>
-      <c r="U240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W240" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X240" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y240" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z240" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>8</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.2583794056110963</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -38661,135 +39415,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB240" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC240" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD240" t="inlineStr">
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE240" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF240" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG240" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH240" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI240" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ240" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK240" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM240" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN240" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP240" t="inlineStr">
-        <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ240" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS240" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="AT240" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV240" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -38821,12 +39508,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -38860,81 +39547,100 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="O241" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="R241" t="n">
-        <v>0.09108458641822616</v>
+        <v>0.5336427512592412</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ241" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR241" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS241" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -38961,17 +39667,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -38996,7 +39702,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -39005,81 +39711,175 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>241</v>
+        <v>30</v>
       </c>
       <c r="O242" t="n">
-        <v>241</v>
-      </c>
-      <c r="R242" t="n">
-        <v>0.06904741899974219</v>
-      </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X242" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB242" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC242" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD242" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE242" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF242" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG242" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH242" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI242" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ242" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK242" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM242" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN242" t="b">
+        <v>1</v>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AR242" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -39111,12 +39911,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -39141,7 +39941,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -39150,17 +39950,22 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="O243" t="n">
-        <v>137</v>
+        <v>49</v>
       </c>
       <c r="R243" t="n">
-        <v>0.11190275183651</v>
+        <v>0.09496052626581025</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO243" t="inlineStr">
@@ -39189,42 +39994,42 @@
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -39256,12 +40061,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -39286,7 +40091,7 @@
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M244" t="inlineStr">
@@ -39295,81 +40100,100 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="O244" t="n">
-        <v>199</v>
+        <v>118</v>
       </c>
       <c r="R244" t="n">
-        <v>0.05701425884211077</v>
+        <v>1.102695890537435</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39396,17 +40220,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -39431,7 +40255,7 @@
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M245" t="inlineStr">
@@ -39440,81 +40264,175 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="O245" t="n">
-        <v>148</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.1208876443197334</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>118</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>Enterohemorragisk E. coli-infektion</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM enterohemorrhagic E. coli category.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
+        <v>1</v>
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ245" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR245" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS245" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_EHEC</t>
+        </is>
+      </c>
       <c r="AT245" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -39576,7 +40494,7 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
@@ -39585,17 +40503,22 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="O246" t="n">
-        <v>165</v>
+        <v>241</v>
       </c>
       <c r="R246" t="n">
-        <v>0.04727312919069485</v>
+        <v>0.06904741899974219</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
@@ -39721,7 +40644,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -39730,13 +40653,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="O247" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="R247" t="n">
-        <v>0.1200708359121676</v>
+        <v>0.11190275183651</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -39866,7 +40789,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -39875,17 +40798,22 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="O248" t="n">
-        <v>185</v>
+        <v>199</v>
       </c>
       <c r="R248" t="n">
-        <v>0.05300320545623363</v>
+        <v>0.05701425884211077</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO248" t="inlineStr">
@@ -40011,7 +40939,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -40020,13 +40948,13 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="O249" t="n">
-        <v>61</v>
+        <v>148</v>
       </c>
       <c r="R249" t="n">
-        <v>0.04982531286151174</v>
+        <v>0.1208876443197334</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -40126,12 +41054,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -40156,109 +41084,95 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N250" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="O250" t="n">
-        <v>1</v>
+        <v>165</v>
       </c>
       <c r="R250" t="n">
-        <v>0.01778809170864137</v>
+        <v>0.04727312919069485</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ250" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40285,17 +41199,17 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -40320,184 +41234,90 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N251" t="n">
-        <v>1</v>
+        <v>147</v>
       </c>
       <c r="O251" t="n">
-        <v>1</v>
-      </c>
-      <c r="U251" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="V251" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
-      <c r="W251" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X251" t="inlineStr">
-        <is>
-          <t>EHEC</t>
-        </is>
-      </c>
-      <c r="Y251" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z251" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA251" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB251" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC251" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD251" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE251" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF251" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG251" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH251" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI251" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ251" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK251" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
-        </is>
-      </c>
-      <c r="AM251" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN251" t="b">
-        <v>1</v>
+        <v>147</v>
+      </c>
+      <c r="R251" t="n">
+        <v>0.1200708359121676</v>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO251" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ251" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR251" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS251" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_535</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -40529,12 +41349,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -40559,26 +41379,31 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
+        <v>185</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>0.05300320545623363</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO252" t="inlineStr">
@@ -40607,42 +41432,890 @@
       </c>
       <c r="AV252" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA252" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB252" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC252" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N253" t="n">
+        <v>61</v>
+      </c>
+      <c r="O253" t="n">
+        <v>61</v>
+      </c>
+      <c r="R253" t="n">
+        <v>0.04982531286151174</v>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP253" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR253" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS253" t="inlineStr"/>
+      <c r="AT253" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU253" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV253" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA253" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB253" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC253" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N254" t="n">
+        <v>9</v>
+      </c>
+      <c r="O254" t="n">
+        <v>9</v>
+      </c>
+      <c r="R254" t="n">
+        <v>0.1600928253777724</v>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO254" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP254" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ254" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR254" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS254" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT254" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU254" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV254" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA254" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB254" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC254" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N255" t="n">
+        <v>9</v>
+      </c>
+      <c r="O255" t="n">
+        <v>9</v>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X255" t="inlineStr">
+        <is>
+          <t>EHEC</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB255" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD255" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE255" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF255" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG255" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH255" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI255" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ255" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK255" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 535.</t>
+        </is>
+      </c>
+      <c r="AM255" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN255" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO255" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP255" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ255" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AR255" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS255" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_535</t>
+        </is>
+      </c>
+      <c r="AT255" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU255" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV255" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA255" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB255" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC255" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N256" t="n">
+        <v>0</v>
+      </c>
+      <c r="O256" t="n">
+        <v>0</v>
+      </c>
+      <c r="R256" t="n">
+        <v>0</v>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP256" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR256" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS256" t="inlineStr"/>
+      <c r="AT256" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU256" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV256" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW252" t="inlineStr">
+      <c r="AW256" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX252" t="inlineStr">
+      <c r="AX256" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY252" t="inlineStr">
+      <c r="AY256" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ252" t="inlineStr">
+      <c r="AZ256" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA252" t="inlineStr">
+      <c r="BA256" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB252" t="inlineStr">
+      <c r="BB256" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC252" t="inlineStr">
+      <c r="BC256" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N257" t="n">
+        <v>209</v>
+      </c>
+      <c r="O257" t="n">
+        <v>209</v>
+      </c>
+      <c r="R257" t="n">
+        <v>0.05987929697488016</v>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP257" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR257" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS257" t="inlineStr"/>
+      <c r="AT257" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU257" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV257" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA257" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB257" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC257" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -40679,7 +42352,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
@@ -40762,7 +42435,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -40772,7 +42445,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>251</v>
+        <v>256</v>
       </c>
     </row>
     <row r="11">
@@ -40792,7 +42465,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -40824,7 +42497,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14323</v>
+        <v>14699</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -39950,13 +39950,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="O243" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="R243" t="n">
-        <v>0.09496052626581025</v>
+        <v>0.1027124059609784</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -41683,13 +41683,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O254" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R254" t="n">
-        <v>0.1600928253777724</v>
+        <v>0.1778809170864138</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -41847,10 +41847,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O255" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -42497,7 +42497,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14699</v>
+        <v>14704</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -39950,13 +39950,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="O243" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="R243" t="n">
-        <v>0.1027124059609784</v>
+        <v>0.1085263157323546</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -41683,13 +41683,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O254" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="R254" t="n">
-        <v>0.1778809170864138</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -41847,10 +41847,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O255" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -42086,13 +42086,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -42316,6 +42316,151 @@
       <c r="BC257" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N258" t="n">
+        <v>122</v>
+      </c>
+      <c r="O258" t="n">
+        <v>122</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.09965062572302348</v>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP258" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR258" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS258" t="inlineStr"/>
+      <c r="AT258" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU258" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV258" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA258" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB258" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC258" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -42352,7 +42497,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -42435,7 +42580,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -42445,7 +42590,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11">
@@ -42497,7 +42642,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14704</v>
+        <v>14834</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d115/2026-2029.xlsx
+++ b/diseases/d115/2026-2029.xlsx
@@ -4151,9 +4151,6 @@
       <c r="O22" t="n">
         <v>12</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.003438045759323263</v>
       </c>
@@ -4452,9 +4449,6 @@
       <c r="O24" t="n">
         <v>136</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.03896451860566364</v>
       </c>
@@ -4748,16 +4742,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="O26" t="n">
-        <v>114</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
+        <v>113</v>
       </c>
       <c r="R26" t="n">
-        <v>0.032661434713571</v>
+        <v>0.03237493090029405</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5054,9 +5045,6 @@
       <c r="O28" t="n">
         <v>97</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.02779086988786304</v>
       </c>
@@ -5355,9 +5343,6 @@
       <c r="O30" t="n">
         <v>100</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.02865038132769385</v>
       </c>
@@ -9024,9 +9009,6 @@
       <c r="O52" t="n">
         <v>117</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.03352094615340181</v>
       </c>
@@ -9325,9 +9307,6 @@
       <c r="O54" t="n">
         <v>90</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.02578534319492447</v>
       </c>
@@ -9626,9 +9605,6 @@
       <c r="O56" t="n">
         <v>99</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.02836387751441691</v>
       </c>
@@ -9927,9 +9903,6 @@
       <c r="O58" t="n">
         <v>116</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.03323444234012487</v>
       </c>
@@ -13605,9 +13578,6 @@
       <c r="O80" t="n">
         <v>125</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.03581297665961732</v>
       </c>
@@ -13906,9 +13876,6 @@
       <c r="O82" t="n">
         <v>134</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.03839151097910976</v>
       </c>
@@ -14207,9 +14174,6 @@
       <c r="O84" t="n">
         <v>112</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.03208842708701712</v>
       </c>
@@ -14508,9 +14472,6 @@
       <c r="O86" t="n">
         <v>132</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.03781850335255588</v>
       </c>
@@ -18189,9 +18150,6 @@
       <c r="O108" t="n">
         <v>152</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.04354857961809466</v>
       </c>
@@ -18490,9 +18448,6 @@
       <c r="O110" t="n">
         <v>112</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.03208842708701712</v>
       </c>
@@ -18791,9 +18746,6 @@
       <c r="O112" t="n">
         <v>148</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.04240256436498691</v>
       </c>
@@ -19092,9 +19044,6 @@
       <c r="O114" t="n">
         <v>140</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.0401105338587714</v>
       </c>
@@ -22773,9 +22722,6 @@
       <c r="O136" t="n">
         <v>130</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.03724549572600201</v>
       </c>
@@ -23074,9 +23020,6 @@
       <c r="O138" t="n">
         <v>150</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.04297557199154078</v>
       </c>
@@ -23375,9 +23318,6 @@
       <c r="O140" t="n">
         <v>162</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.04641361775086404</v>
       </c>
@@ -23676,9 +23616,6 @@
       <c r="O142" t="n">
         <v>63</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.01804974023644713</v>
       </c>
@@ -42461,6 +42398,156 @@
       <c r="BC258" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>shiga-toxin-producing-escherichia-coli-infection</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N259" t="n">
+        <v>175</v>
+      </c>
+      <c r="O259" t="n">
+        <v>175</v>
+      </c>
+      <c r="R259" t="n">
+        <v>0.05013816732346424</v>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO259" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP259" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR259" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS259" t="inlineStr"/>
+      <c r="AT259" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU259" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV259" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA259" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB259" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC259" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -42497,7 +42584,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
@@ -42580,7 +42667,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -42590,7 +42677,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -42642,7 +42729,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14834</v>
+        <v>15008</v>
       </c>
     </row>
     <row r="16">
